--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_410_Korea_South.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_410_Korea_South.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rc23847b95fb84701"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R137192fc292642d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ra5534c8c009a4d15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R7e23ae7112394982"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R608065ee575c445e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rcadd6cb5a01b425e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R402a2d16d90a4942"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R2505f61fd6a84242"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R6fd12384fb714293"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rc38a4221d5f941c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R88bcbdcda6e04cbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R885d2c43b9eb4ba5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ410CommercialTable" displayName="EEZ410CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ410CommercialTable" displayName="EEZ410CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ410FunctionalTable" displayName="EEZ410FunctionalTable" ref="A1:O22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O22"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ410FunctionalTable" displayName="EEZ410FunctionalTable" ref="A1:E22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E22"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ410ValidationTable" displayName="EEZ410ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ410ValidationTable" displayName="EEZ410ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -8600,7 +8554,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe7f7e110d1c4491"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafc068e923134a9d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8610,20 +8564,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8631,714 +8575,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>216873.10867444647</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.140253711823549</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>138.11909111099976</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>216873.10867444647</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>138.12490368198664</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$119,A2,'Species'!$U$2:$U$119))</x:f>
-        <x:v>29955577.24687094</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.140253711823549</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>138.11909111099976</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>29954316.656531624</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1260.5903393141925</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0000420837622093</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.000042083762209254646</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>8694.1696922511</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.158641825165637</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1440.9264888773512</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>8694.1696922511</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1442.2623302501108</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$119,A3,'Species'!$U$2:$U$119))</x:f>
-        <x:v>12539273.43993596</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.158641825165637</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1440.9264888773512</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>12527659.408359258</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>11614.031576702371</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0009270711469815</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0009270711469815938</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>133314.9246035074</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.9376076730289915</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>86.6179045317135</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>133314.9246035074</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>176.0493191635867</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$119,A4,'Species'!$U$2:$U$119))</x:f>
-        <x:v>23470001.710792366</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.9376076730289915</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>86.6179045317135</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>11547459.411959186</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>11922542.29883318</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>2.032481853669521</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>1.0324818536695213</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>33761.2940928235</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.498221755022576</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>314.93559956817035</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>33761.2940928235</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>542.8558794420477</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$119,A5,'Species'!$U$2:$U$119))</x:f>
-        <x:v>18327516.99586131</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.498221755022576</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>314.93559956817035</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>10632633.397320695</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>7694883.598540615</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.7237044023806596</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.7237044023806595</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>47265.973078989</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.109111471145805</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>128.56165991236077</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>47265.973078989</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>149.59362517636785</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$119,A6,'Species'!$U$2:$U$119))</x:f>
-        <x:v>7070688.260374574</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.109111471145805</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>128.56165991236077</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>6076591.956407784</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>994096.3039667904</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1635943817024792</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.1635943817024793</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>75338.6213811257</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0144795665147983</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.339024548945368</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>75338.6213811257</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>10.590211456326854</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$119,A7,'Species'!$U$2:$U$119))</x:f>
-        <x:v>797851.9312542686</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0144795665147983</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.339024548945368</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>778927.855943159</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>18924.075311109656</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0242950295932036</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.024295029593203572</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>532262.3346641831</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.4628785321339337</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>290.3210541659802</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>532262.3346641831</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>523.9702800564205</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$119,A8,'Species'!$U$2:$U$119))</x:f>
-        <x:v>278889644.5574762</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.4628785321339337</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>290.3210541659802</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>154526962.09255135</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>124362682.46492487</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.8047960095820683</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.8047960095820683</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>620944.6986004841</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6835115213763885</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>482.5157805267033</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>620944.6986004841</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>968.7750842608438</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$119,A9,'Species'!$U$2:$U$119))</x:f>
-        <x:v>601555752.7080082</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6835115213763885</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>482.5157805267033</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>299615615.9091311</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>301940136.79887706</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>2.0077583435786304</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.0077583435786301</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>100</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>199.52623149688787</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>199.52623149688787</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$119,A10,'Species'!$U$2:$U$119))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>19952.62314968879</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.3</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>199.52623149688787</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>19952.62314968879</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>15686.356244184199</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.718155621620105</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>522.583413824445</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>15686.356244184199</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>553.1368622018293</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$119,A11,'Species'!$U$2:$U$119))</x:f>
-        <x:v>8676701.87228812</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.718155621620105</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>522.583413824445</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>8197429.596552177</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>479272.2757359436</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0584661655328549</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0584661655328549</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>197.0068597637</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.050007872042485</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1122.0387922462844</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>197.0068597637</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1122.0477567385437</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$119,A12,'Species'!$U$2:$U$119))</x:f>
-        <x:v>221051.10505996447</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.050007872042485</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1122.0387922462844</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>221049.33899349507</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1.7660664693976287</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0000079894673173</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.000007989467317292452</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>7700.4268931418</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.411897452857829</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2581.6505302469363</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>7700.4268931418</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2584.2898767835172</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$119,A13,'Species'!$U$2:$U$119))</x:f>
-        <x:v>19900135.266857903</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.411897452857829</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2581.6505302469363</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>19879811.171807297</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>20324.095050606877</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0010223484959169</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.0010223484959167844</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6e3375d2164409c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28c5b5f7dd2b47b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9348,20 +8828,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -9369,1200 +8839,421 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>113649.64052341969</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.959705063715416</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>911.3916885623521</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>113649.64052341969</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1167.5487120529301</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$119,A2,'Species'!$U$2:$U$119))</x:f>
-        <x:v>132691491.41839716</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.959705063715416</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>911.3916885623521</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>103579337.78114378</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>29112153.637253374</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.2810613995116034</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.28106139951160347</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1499.1624205657</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.01</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>102.32929922807536</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1499.1624205657</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>102.32929922807536</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$119,A3,'Species'!$U$2:$U$119))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>153408.23992555327</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.01</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>102.32929922807536</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>153408.23992555327</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>133610.0838328441</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.231173677082296</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1702.8393483661537</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>133610.0838328441</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2397.8748456144613</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$119,A4,'Species'!$U$2:$U$119))</x:f>
-        <x:v>320380259.14321625</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.231173677082296</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1702.8393483661537</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>227516508.08906743</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>92863751.05414882</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.408162694804523</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.40816269480452305</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>47216.3230354895</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.179782885430325</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1512.8047707814872</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>47216.3230354895</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1758.1982177248885</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$119,A5,'Species'!$U$2:$U$119))</x:f>
-        <x:v>83015655.00852023</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.179782885430325</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1512.8047707814872</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>71429078.74684834</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>11586576.261671886</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1622109155675358</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.16221091556753583</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>4106.9999999999</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.25</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1778.2794100389228</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>4106.9999999999</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1778.2794100389228</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$119,A6,'Species'!$U$2:$U$119))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>7303393.537029678</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.25</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1778.2794100389228</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>7303393.537029678</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>52188.866018057095</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.46789462542594</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2936.9369649653836</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>52188.866018057095</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2959.3600795645993</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$119,A7,'Species'!$U$2:$U$119))</x:f>
-        <x:v>154445646.69158366</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.46789462542594</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2936.9369649653836</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>153275409.76805764</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1170236.9235260189</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.00763486410049</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.007634864100489878</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>9170.0175458555</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.690717192334114</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>490.5883065445813</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>9170.0175458555</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>550.3267646766373</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$119,A8,'Species'!$U$2:$U$119))</x:f>
-        <x:v>5046506.088038655</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.690717192334114</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>490.5883065445813</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>4498703.378805348</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>547802.7092333073</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1217690216728133</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.12176902167281341</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>197.0068597637</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.050007872042485</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1122.0387922462844</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>197.0068597637</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1122.0477567385437</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$119,A9,'Species'!$U$2:$U$119))</x:f>
-        <x:v>221051.10505996447</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.050007872042485</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1122.0387922462844</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>221049.33899349507</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1.7660664693976287</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0000079894673173</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.000007989467317292452</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>36374.9964120536</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.4287297440291997</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>268.3673909557461</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>36374.9964120536</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>381.42619580763795</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$119,A10,'Species'!$U$2:$U$119))</x:f>
-        <x:v>13874376.503966086</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.4287297440291997</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>268.3673909557461</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>9761862.883127451</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>4112513.6208386347</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.421283690426216</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.4212836904262161</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>102675.66852045292</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.5314727781478155</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>339.9951940228469</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>102675.66852045292</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>354.3547020377907</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$119,A11,'Species'!$U$2:$U$119))</x:f>
-        <x:v>36383605.92509606</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.5314727781478155</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>339.9951940228469</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>34909233.8400369</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1474372.0850591585</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0422344440962272</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.042234444096227126</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>426908.9792123623</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.3546697906090976</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>226.29230732033142</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>426908.9792123623</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>267.0310303566345</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$119,A12,'Species'!$U$2:$U$119))</x:f>
-        <x:v>113997944.58757618</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.3546697906090976</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>226.29230732033142</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>96606217.92173287</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>17391726.665843308</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1800269903944849</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.18002699039448478</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>203565.184544647</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.3315514622421776</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>214.5613347763202</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>203565.184544647</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>235.4445263153683</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$119,A13,'Species'!$U$2:$U$119))</x:f>
-        <x:v>47928308.449414946</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.3315514622421776</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>214.5613347763202</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>43677217.70988741</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>4251090.739527538</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0973297055633011</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.09732970556330102</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>44521.264424598296</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.160482077682313</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>144.70451356938477</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>44521.264424598296</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>317.990360978522</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$119,A14,'Species'!$U$2:$U$119))</x:f>
-        <x:v>14157332.945598243</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.160482077682313</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>144.70451356938477</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>6442427.912055451</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>7714905.033542791</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>2.197515150942738</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>1.1975151509427377</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>90837.80149933779</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.082440538924846</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>12.090396369338276</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>90837.80149933779</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>13.225033240338114</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$119,A15,'Species'!$U$2:$U$119))</x:f>
-        <x:v>1201332.9443079776</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.082440538924846</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>12.090396369338276</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>1098265.0254462645</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>103067.91886171303</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0938461268215591</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.09384612682155914</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>96939.92819145382</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.753322787494199</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>56.6660300377391</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>96939.92819145382</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>98.98527248622649</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$119,A16,'Species'!$U$2:$U$119))</x:f>
-        <x:v>9595625.206826285</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.753322787494199</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>56.6660300377391</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>5493200.882753193</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>4102424.324073091</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.7468185510843643</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.7468185510843643</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small bathydemersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>3066.0000000002997</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.51</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>323.5936569296281</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>3066.0000000002997</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$119,A17,'Species'!$U$2:$U$119))</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>992138.1521463366</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.51</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
-        <x:v>992138.1521463366</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>8678.0000000002</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.62</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>416.8693834703355</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>8678.0000000002</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$119,A18,'Species'!$U$2:$U$119))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>3617592.5097556547</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.62</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>3617592.5097556547</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>37738.9802837151</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.27542602523444</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>188.54977792804277</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>37738.9802837151</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>265.57232931757636</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$119,A19,'Species'!$U$2:$U$119))</x:f>
-        <x:v>10022428.900016308</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.27542602523444</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>188.54977792804277</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>7115676.351725266</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>2906752.5482910415</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.4084998255417098</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.4084998255417098</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>248619.68245850058</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.1505336992067803</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>141.4274461851243</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>248619.68245850058</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>141.79651063067354</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$119,A20,'Species'!$U$2:$U$119))</x:f>
-        <x:v>35253403.44672146</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.1505336992067803</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>141.4274461851243</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>35161646.76146228</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>91756.68525917828</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0026095673471058</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.002609567347105741</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>920.0349089593</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.1099999999999994</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>128.82495516931323</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>920.0349089593</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$119,A21,'Species'!$U$2:$U$119))</x:f>
-        <x:v>118523.45590088512</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.1099999999999994</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>128.82495516931323</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>118523.45590088499</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>1.3096723705530167e-10</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>1.104990029693555e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>29654.2940928236</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.3941035034648896</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>247.80125609346175</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>29654.2940928236</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>371.754708587027</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$119,A22,'Species'!$U$2:$U$119))</x:f>
-        <x:v>11024123.458831633</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.3941035034648896</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>247.80125609346175</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>7348371.324766611</x:v>
       </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>3675752.1340650218</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.5002131726354706</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.5002131726354705</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G22">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O22">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R219bd919f3b94257"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ed49fef94de4f7c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10737,7 +9428,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -10836,7 +9527,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>1001424147.7179291</x:v>
+        <x:v>553978409.4187069</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10850,7 +9541,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>1001424147.7179292</x:v>
+        <x:v>820319263.610668</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10864,7 +9555,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-2.384185791015625e-7</x:v>
+        <x:v>-447445738.29922247</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10878,7 +9569,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-1.1920928955078125e-7</x:v>
+        <x:v>-181104884.10726142</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10889,9 +9580,9 @@
         <x:v>EEZ_410</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -10903,47 +9594,19 @@
         <x:v>EEZ_410</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_410</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_410</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27c6e37a74504ec3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62ea9e8d81504fa1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10990,7 +9653,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
